--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9105-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9105-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D62D518-87A0-4570-A408-2070B56C50D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9FF6DAC-4FE8-488D-873F-DD82C0D5FBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E6F83575-65AA-494E-8C30-096B34976B9D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{FF779738-ECFA-4983-944F-A0DD4BC696A1}"/>
   </bookViews>
   <sheets>
     <sheet name="9105-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1568,25 +1568,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08C84A9-16EB-4B7B-ABF5-F1487DE3F733}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E689225-B5B7-40EE-B4AC-DD4DDE48D478}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1656,7 +1656,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1776,7 +1776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2023</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="39">
         <v>2022</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2020</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2019</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2018</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2017</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2016</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>29</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2015</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2014</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2013</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="43"/>
       <c r="B36" s="44"/>
       <c r="C36" s="20" t="s">
@@ -4072,7 +4072,7 @@
       <c r="W36" s="50"/>
       <c r="X36" s="46"/>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>2012</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>5.72</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2011</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>2010</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2009</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2008</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2007</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>2006</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2005</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>2004</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2003</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39" t="s">
         <v>65</v>
       </c>
